--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(309)_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(309)_2026-02.xlsx
@@ -1606,31 +1606,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>58</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10477500" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2845,7 +2820,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3197,13 +3172,13 @@
         <v>1762.41</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>43.2882933</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>1.76</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>24.56</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3237,13 +3212,13 @@
         <v>2974.62</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>25.0202211</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>2.97</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>8.41</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3417,13 +3392,13 @@
         <v>4338.21</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>12.7249662</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>4.34</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3437,13 +3412,13 @@
         <v>4286.43</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>20.7750963</v>
+        <v>14.8071972</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>4.29</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3457,13 +3432,13 @@
         <v>4225.98</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>58.2140127</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>4.23</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>13.78</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3477,13 +3452,13 @@
         <v>3117.33</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>8.420476499999999</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>3.12</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3497,13 +3472,13 @@
         <v>65626.05</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>1622.19</v>
+        <v>1763.89</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>65.66</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>24.72</v>
+        <v>26.88</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3602,7 +3577,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>1622.19</v>
+        <v>1763.89</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3707,7 +3682,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
